--- a/data/travel.xlsx
+++ b/data/travel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguellunet/Desktop/miguellunet.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D81998B-81E9-FF45-BF73-5795474D5FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9879700-DF96-5A4F-945A-20809C776D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18220" yWindow="29460" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13640,7 +13640,7 @@
         <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G75" vm="121">
         <v>50.8466666666667</v>

--- a/data/travel.xlsx
+++ b/data/travel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inesctecpt-my.sharepoint.com/personal/miguel_lunet_inesctec_pt/Documents/miguellunet.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{F9879700-DF96-5A4F-945A-20809C776D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2304D95-AFEE-6A44-B2D5-1B5766C7AB86}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="13_ncr:1_{F9879700-DF96-5A4F-945A-20809C776D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4406BF47-284B-F942-8155-02723B197348}"/>
   <bookViews>
-    <workbookView xWindow="18220" yWindow="29460" windowWidth="29400" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="188">
+  <futureMetadata name="XLRICHVALUE" count="186">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -321,21 +321,21 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="181"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="185"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="188"/>
+          <xlrd:rvb i="183"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="187"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="190"/>
         </ext>
       </extLst>
     </bk>
@@ -1112,20 +1112,6 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="640"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="644"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="647"/>
         </ext>
       </extLst>
@@ -1355,7 +1341,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <valueMetadata count="188">
+  <valueMetadata count="186">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1913,12 +1899,6 @@
     </bk>
     <bk>
       <rc t="1" v="185"/>
-    </bk>
-    <bk>
-      <rc t="1" v="186"/>
-    </bk>
-    <bk>
-      <rc t="1" v="187"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2321,6 +2301,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2368,20 +2351,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2394,6 +2377,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2909,7 +2896,7 @@
     <v t="r">172</v>
   </a>
   <a r="1">
-    <v t="r">182</v>
+    <v t="r">184</v>
   </a>
   <a r="1">
     <v t="r">194</v>
@@ -4329,45 +4316,45 @@
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Naples</v>
-    <v>36544722-9267-f7ae-0f6f-d482d29969f2</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Campania</v>
-    <v>9933ef2b-24f2-a29d-6e4f-fe6bffe78694</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Metropolitan City of Naples</v>
-    <v>aeb76b48-07bf-43a8-8941-86d06bb8bf02</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>119.02</fb>
+    <v>Reykjavík</v>
+    <v>8b129243-97ea-2b6a-4e18-4d73fc81ebf1</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Capital Region</v>
+    <v>d2dc41c5-6862-b127-c3f3-e44b773cc325</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>274.53873969599999</fb>
     <v>8</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Iceland</v>
+    <v>78349f27-a762-88a8-61d6-3bc8a5b105b5</v>
+    <v>en-US</v>
+    <v>Map</v>
   </rv>
   <rv s="2">
     <v>14</v>
     <v>6</v>
-    <v>51</v>
+    <v>52</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Naples</v>
-  </rv>
-  <rv s="1">
-    <fb>40.835833333333298</fb>
+    <v>Image of Reykjavík</v>
+  </rv>
+  <rv s="1">
+    <fb>64.147499999999994</fb>
     <v>9</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Gaetano Manfredi (Mayor)</v>
-    <v>9955adec-7820-a4a2-b679-508e30abc592</v>
+    <v>Dagur B. Eggertsson (Mayor)</v>
+    <v>6fdc1913-cf77-4e9c-a4f1-54fb748f52ad</v>
     <v>en-US</v>
     <v>Generic</v>
   </rv>
@@ -4375,43 +4362,130 @@
     <v>19</v>
   </rv>
   <rv s="4">
-    <v>https://www.bing.com/search?q=naples+italy&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=reykjavik+iceland&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
   <rv s="1">
-    <fb>14.248611111111099</fb>
+    <fb>-21.934999999999999</fb>
     <v>9</v>
   </rv>
   <rv s="1">
-    <fb>909048</fb>
+    <fb>139875</fb>
     <v>8</v>
   </rv>
-  <rv s="8">
+  <rv s="6">
     <v>#VALUE!</v>
-    <v>52</v>
-    <v>22</v>
-    <v>Naples</v>
+    <v>53</v>
+    <v>12</v>
+    <v>Reykjavík</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>7</v>
-    <v>en-US</v>
-    <v>36544722-9267-f7ae-0f6f-d482d29969f2</v>
+    <v>23</v>
+    <v>en-US</v>
+    <v>8b129243-97ea-2b6a-4e18-4d73fc81ebf1</v>
     <v>536870912</v>
     <v>1</v>
     <v>167</v>
     <v>168</v>
     <v>169</v>
-    <v>62</v>
-    <v>Naples is the regional capital of Campania and the third-largest city of Italy, after Rome and Milan, with a population of 909,048 within the city's administrative limits as of 2022. Its province-level municipality is the third most populous ...</v>
+    <v>Reykjavík is the capital and largest city of Iceland. It is located in southwestern Iceland, on the southern shore of Faxaflói bay. With a latitude of 64°08′ N, the city is the world's northernmost capital of a sovereign state. Reykjavík has a ...</v>
     <v>170</v>
     <v>171</v>
     <v>173</v>
     <v>174</v>
     <v>175</v>
+    <v>Reykjavík</v>
+    <v>176</v>
+    <v>Reykjavík</v>
+    <v>mdp/vdpid/5441531491869786113</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Naples</v>
-    <v>176</v>
+    <v>36544722-9267-f7ae-0f6f-d482d29969f2</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Campania</v>
+    <v>9933ef2b-24f2-a29d-6e4f-fe6bffe78694</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Metropolitan City of Naples</v>
+    <v>aeb76b48-07bf-43a8-8941-86d06bb8bf02</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>119.02</fb>
+    <v>8</v>
+  </rv>
+  <rv s="2">
+    <v>15</v>
+    <v>6</v>
+    <v>54</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Naples</v>
+  </rv>
+  <rv s="1">
+    <fb>40.835833333333298</fb>
+    <v>9</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Gaetano Manfredi (Mayor)</v>
+    <v>9955adec-7820-a4a2-b679-508e30abc592</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>20</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=naples+italy&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>14.248611111111099</fb>
+    <v>9</v>
+  </rv>
+  <rv s="1">
+    <fb>909048</fb>
+    <v>8</v>
+  </rv>
+  <rv s="8">
+    <v>#VALUE!</v>
+    <v>55</v>
+    <v>22</v>
+    <v>Naples</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>7</v>
+    <v>en-US</v>
+    <v>36544722-9267-f7ae-0f6f-d482d29969f2</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>179</v>
+    <v>180</v>
+    <v>181</v>
+    <v>62</v>
+    <v>Naples is the regional capital of Campania and the third-largest city of Italy, after Rome and Milan, with a population of 909,048 within the city's administrative limits as of 2022. Its province-level municipality is the third most populous ...</v>
+    <v>182</v>
+    <v>183</v>
+    <v>185</v>
+    <v>186</v>
+    <v>187</v>
+    <v>Naples</v>
+    <v>188</v>
     <v>70</v>
     <v>Naples</v>
     <v>mdp/vdpid/7216548829858889729</v>
@@ -4426,94 +4500,6 @@
   <rv s="1">
     <fb>5.7</fb>
     <v>8</v>
-  </rv>
-  <rv s="2">
-    <v>15</v>
-    <v>6</v>
-    <v>53</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Amalfi</v>
-  </rv>
-  <rv s="1">
-    <fb>40.633333333332999</fb>
-    <v>9</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Daniele Milano (Mayor)</v>
-    <v>981fd7f7-abe7-8f39-76ed-5bf2fa98ace0</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="3">
-    <v>20</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=amalfi&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>14.602777777778</fb>
-    <v>9</v>
-  </rv>
-  <rv s="1">
-    <fb>5102</fb>
-    <v>8</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>54</v>
-    <v>2</v>
-    <v>Amalfi</v>
-    <v>4</v>
-    <v>5</v>
-    <v>Map</v>
-    <v>6</v>
-    <v>35</v>
-    <v>en-US</v>
-    <v>a4d4a24a-a151-00bf-28f4-03342fdffc11</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>167</v>
-    <v>179</v>
-    <v>62</v>
-    <v>Amalfi is a town and comune in the province of Salerno, in the region of Campania, Italy, on the Gulf of Salerno. It lies at the mouth of a deep ravine, at the foot of Monte Cerreto, surrounded by dramatic cliffs and coastal scenery. The town of ...</v>
-    <v>180</v>
-    <v>181</v>
-    <v>183</v>
-    <v>184</v>
-    <v>185</v>
-    <v>Amalfi</v>
-    <v>186</v>
-    <v>70</v>
-    <v>Amalfi</v>
-    <v>mdp/vdpid/7216749330357551106</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Reykjavík</v>
-    <v>8b129243-97ea-2b6a-4e18-4d73fc81ebf1</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Capital Region</v>
-    <v>d2dc41c5-6862-b127-c3f3-e44b773cc325</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>274.53873969599999</fb>
-    <v>8</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Iceland</v>
-    <v>78349f27-a762-88a8-61d6-3bc8a5b105b5</v>
-    <v>en-US</v>
-    <v>Map</v>
   </rv>
   <rv s="2">
     <v>16</v>
@@ -4521,16 +4507,16 @@
     <v>56</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Reykjavík</v>
-  </rv>
-  <rv s="1">
-    <fb>64.147499999999994</fb>
+    <v>Image of Amalfi</v>
+  </rv>
+  <rv s="1">
+    <fb>40.633333333332999</fb>
     <v>9</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Dagur B. Eggertsson (Mayor)</v>
-    <v>6fdc1913-cf77-4e9c-a4f1-54fb748f52ad</v>
+    <v>Daniele Milano (Mayor)</v>
+    <v>981fd7f7-abe7-8f39-76ed-5bf2fa98ace0</v>
     <v>en-US</v>
     <v>Generic</v>
   </rv>
@@ -4538,44 +4524,45 @@
     <v>21</v>
   </rv>
   <rv s="4">
-    <v>https://www.bing.com/search?q=reykjavik+iceland&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=amalfi&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
   <rv s="1">
-    <fb>-21.934999999999999</fb>
+    <fb>14.602777777778</fb>
     <v>9</v>
   </rv>
   <rv s="1">
-    <fb>139875</fb>
+    <fb>5102</fb>
     <v>8</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>#VALUE!</v>
     <v>57</v>
-    <v>12</v>
-    <v>Reykjavík</v>
+    <v>2</v>
+    <v>Amalfi</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>23</v>
-    <v>en-US</v>
-    <v>8b129243-97ea-2b6a-4e18-4d73fc81ebf1</v>
+    <v>35</v>
+    <v>en-US</v>
+    <v>a4d4a24a-a151-00bf-28f4-03342fdffc11</v>
     <v>536870912</v>
     <v>1</v>
-    <v>189</v>
-    <v>190</v>
+    <v>179</v>
     <v>191</v>
-    <v>Reykjavík is the capital and largest city of Iceland. It is located in southwestern Iceland, on the southern shore of Faxaflói bay. With a latitude of 64°08′ N, the city is the world's northernmost capital of a sovereign state. Reykjavík has a ...</v>
+    <v>62</v>
+    <v>Amalfi is a town and comune in the province of Salerno, in the region of Campania, Italy, on the Gulf of Salerno. It lies at the mouth of a deep ravine, at the foot of Monte Cerreto, surrounded by dramatic cliffs and coastal scenery. The town of ...</v>
     <v>192</v>
     <v>193</v>
     <v>195</v>
     <v>196</v>
     <v>197</v>
-    <v>Reykjavík</v>
+    <v>Amalfi</v>
     <v>198</v>
-    <v>Reykjavík</v>
-    <v>mdp/vdpid/5441531491869786113</v>
+    <v>70</v>
+    <v>Amalfi</v>
+    <v>mdp/vdpid/7216749330357551106</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
@@ -10664,21 +10651,44 @@
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://fr.wikipedia.org/wiki/Reykjavik	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Reykjav%C3%ADk	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="1">
+      <v>51</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+      <v>52</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
       <v xml:space="preserve">https://en.wikipedia.org/wiki/Naples	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="10">
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
-      <v>51</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
+      <v>54</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
@@ -10687,30 +10697,7 @@
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="1">
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-      <v>53</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://fr.wikipedia.org/wiki/Reykjavik	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://en.wikipedia.org/wiki/Reykjav%C3%ADk	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="1">
-      <v>55</v>
+      <v>56</v>
       <v>56</v>
       <v>56</v>
       <v>56</v>
@@ -12127,11 +12114,11 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year"/>
     <tableColumn id="7" xr3:uid="{C4EE25A0-3E05-5F4E-BC5E-5526B9FF538D}" name="Month number"/>
-    <tableColumn id="8" xr3:uid="{5B3572D1-C895-B94A-9A76-394322945922}" name="Column1" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{5B3572D1-C895-B94A-9A76-394322945922}" name="Column1" dataDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{D36CA8D0-96D7-FA45-A7FD-B2A92CE3C891}" name="City" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{D36CA8D0-96D7-FA45-A7FD-B2A92CE3C891}" name="City" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="City-map"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Country"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Context"/>
@@ -12966,35 +12953,35 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
-        <v>2019.75</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>2018.5833333333333</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="F16" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I16" vm="38">
-        <v>40.835833333333298</v>
+        <v>64.147499999999994</v>
       </c>
       <c r="J16" vm="39">
-        <v>14.248611111111099</v>
+        <v>-21.934999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -13012,7 +12999,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" t="e" vm="40">
         <v>#VALUE!</v>
@@ -13024,43 +13011,43 @@
         <v>6</v>
       </c>
       <c r="I17" vm="41">
-        <v>40.633333333332999</v>
+        <v>40.835833333333298</v>
       </c>
       <c r="J17" vm="42">
-        <v>14.602777777778</v>
+        <v>14.248611111111099</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
-        <v>2021.5833333333333</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>66</v>
+        <v>2019.75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="F18" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="I18" vm="44">
-        <v>64.147499999999994</v>
+        <v>40.633333333332999</v>
       </c>
       <c r="J18" vm="45">
-        <v>-21.934999999999999</v>
+        <v>14.602777777778</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -14508,11 +14495,11 @@
       <c r="H62" t="s">
         <v>6</v>
       </c>
-      <c r="I62" vm="154">
-        <v>42.0075</v>
-      </c>
-      <c r="J62" vm="155">
-        <v>13.280833333333</v>
+      <c r="I62" s="4">
+        <v>38.640388000000002</v>
+      </c>
+      <c r="J62" s="4">
+        <v>34.846305999999998</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -14565,7 +14552,7 @@
       <c r="E64" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F64" t="e" vm="156">
+      <c r="F64" t="e" vm="154">
         <v>#VALUE!</v>
       </c>
       <c r="G64" t="s">
@@ -14574,10 +14561,10 @@
       <c r="H64" t="s">
         <v>8</v>
       </c>
-      <c r="I64" vm="157">
+      <c r="I64" vm="155">
         <v>41.3825</v>
       </c>
-      <c r="J64" vm="158">
+      <c r="J64" vm="156">
         <v>2.1769444444444002</v>
       </c>
     </row>
@@ -14598,7 +14585,7 @@
       <c r="E65" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F65" t="e" vm="159">
+      <c r="F65" t="e" vm="157">
         <v>#VALUE!</v>
       </c>
       <c r="G65" t="s">
@@ -14607,10 +14594,10 @@
       <c r="H65" t="s">
         <v>30</v>
       </c>
-      <c r="I65" vm="160">
+      <c r="I65" vm="158">
         <v>46.066666669999996</v>
       </c>
-      <c r="J65" vm="161">
+      <c r="J65" vm="159">
         <v>11.116666670000001</v>
       </c>
     </row>
@@ -14631,7 +14618,7 @@
       <c r="E66" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F66" t="e" vm="162">
+      <c r="F66" t="e" vm="160">
         <v>#VALUE!</v>
       </c>
       <c r="G66" t="s">
@@ -14640,10 +14627,10 @@
       <c r="H66" t="s">
         <v>30</v>
       </c>
-      <c r="I66" vm="163">
+      <c r="I66" vm="161">
         <v>36.716666666667003</v>
       </c>
-      <c r="J66" vm="164">
+      <c r="J66" vm="162">
         <v>-4.4166666666666998</v>
       </c>
     </row>
@@ -14664,7 +14651,7 @@
       <c r="E67" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F67" t="e" vm="165">
+      <c r="F67" t="e" vm="163">
         <v>#VALUE!</v>
       </c>
       <c r="G67" t="s">
@@ -14673,10 +14660,10 @@
       <c r="H67" t="s">
         <v>30</v>
       </c>
-      <c r="I67" vm="166">
+      <c r="I67" vm="164">
         <v>41.983333333333</v>
       </c>
-      <c r="J67" vm="167">
+      <c r="J67" vm="165">
         <v>2.8166666666667002</v>
       </c>
     </row>
@@ -14697,7 +14684,7 @@
       <c r="E68" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F68" t="e" vm="156">
+      <c r="F68" t="e" vm="154">
         <v>#VALUE!</v>
       </c>
       <c r="G68" t="s">
@@ -14706,10 +14693,10 @@
       <c r="H68" t="s">
         <v>30</v>
       </c>
-      <c r="I68" vm="157">
+      <c r="I68" vm="155">
         <v>41.3825</v>
       </c>
-      <c r="J68" vm="158">
+      <c r="J68" vm="156">
         <v>2.1769444444444002</v>
       </c>
     </row>
@@ -14730,7 +14717,7 @@
       <c r="E69" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F69" t="e" vm="168">
+      <c r="F69" t="e" vm="166">
         <v>#VALUE!</v>
       </c>
       <c r="G69" t="s">
@@ -14763,7 +14750,7 @@
       <c r="E70" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F70" t="e" vm="169">
+      <c r="F70" t="e" vm="167">
         <v>#VALUE!</v>
       </c>
       <c r="G70" t="s">
@@ -14772,10 +14759,10 @@
       <c r="H70" t="s">
         <v>13</v>
       </c>
-      <c r="I70" vm="170">
+      <c r="I70" vm="168">
         <v>45.566388888889001</v>
       </c>
-      <c r="J70" vm="171">
+      <c r="J70" vm="169">
         <v>5.9208333333332996</v>
       </c>
     </row>
@@ -14796,7 +14783,7 @@
       <c r="E71" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F71" t="e" vm="172">
+      <c r="F71" t="e" vm="170">
         <v>#VALUE!</v>
       </c>
       <c r="G71" t="s">
@@ -14805,10 +14792,10 @@
       <c r="H71" t="s">
         <v>13</v>
       </c>
-      <c r="I71" vm="173">
+      <c r="I71" vm="171">
         <v>45.758888888888997</v>
       </c>
-      <c r="J71" vm="174">
+      <c r="J71" vm="172">
         <v>4.8413888888888996</v>
       </c>
     </row>
@@ -14829,7 +14816,7 @@
       <c r="E72" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F72" t="e" vm="175">
+      <c r="F72" t="e" vm="173">
         <v>#VALUE!</v>
       </c>
       <c r="G72" t="s">
@@ -14838,10 +14825,10 @@
       <c r="H72" t="s">
         <v>30</v>
       </c>
-      <c r="I72" vm="176">
+      <c r="I72" vm="174">
         <v>69.649609999999996</v>
       </c>
-      <c r="J72" vm="177">
+      <c r="J72" vm="175">
         <v>18.95701</v>
       </c>
     </row>
@@ -14862,7 +14849,7 @@
       <c r="E73" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F73" t="e" vm="178">
+      <c r="F73" t="e" vm="176">
         <v>#VALUE!</v>
       </c>
       <c r="G73" t="s">
@@ -14871,10 +14858,10 @@
       <c r="H73" t="s">
         <v>30</v>
       </c>
-      <c r="I73" vm="179">
+      <c r="I73" vm="177">
         <v>45.406388888888998</v>
       </c>
-      <c r="J73" vm="180">
+      <c r="J73" vm="178">
         <v>11.877777777778</v>
       </c>
     </row>
@@ -14918,7 +14905,7 @@
       <c r="B75">
         <v>6</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
         <v>2026.5</v>
       </c>
@@ -14928,7 +14915,7 @@
       <c r="E75" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F75" t="e" vm="181">
+      <c r="F75" t="e" vm="179">
         <v>#VALUE!</v>
       </c>
       <c r="G75" t="s">
@@ -14951,7 +14938,7 @@
       <c r="B76">
         <v>6</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
         <v>2026.5</v>
       </c>
@@ -14961,7 +14948,7 @@
       <c r="E76" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F76" t="e" vm="181">
+      <c r="F76" t="e" vm="179">
         <v>#VALUE!</v>
       </c>
       <c r="G76" t="s">
@@ -14984,7 +14971,7 @@
       <c r="B77">
         <v>6</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
         <v>2026.5</v>
       </c>
@@ -14994,7 +14981,7 @@
       <c r="E77" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F77" t="e" vm="182">
+      <c r="F77" t="e" vm="180">
         <v>#VALUE!</v>
       </c>
       <c r="G77" t="s">
@@ -15017,7 +15004,7 @@
       <c r="B78">
         <v>7</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
         <v>2026.5833333333333</v>
       </c>
@@ -15027,7 +15014,7 @@
       <c r="E78" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F78" t="e" vm="183">
+      <c r="F78" t="e" vm="181">
         <v>#VALUE!</v>
       </c>
       <c r="G78" t="s">
@@ -15050,7 +15037,7 @@
       <c r="B79">
         <v>7</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79">
         <f>Table1[[#This Row],[Year]]+Table1[[#This Row],[Month number]]/12</f>
         <v>2026.5833333333333</v>
       </c>
@@ -15060,7 +15047,7 @@
       <c r="E79" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F79" t="e" vm="184">
+      <c r="F79" t="e" vm="182">
         <v>#VALUE!</v>
       </c>
       <c r="G79" t="s">
@@ -15093,7 +15080,7 @@
       <c r="E80" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F80" t="e" vm="185">
+      <c r="F80" t="e" vm="183">
         <v>#VALUE!</v>
       </c>
       <c r="G80" t="s">
@@ -15126,7 +15113,7 @@
       <c r="E81" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F81" t="e" vm="186">
+      <c r="F81" t="e" vm="184">
         <v>#VALUE!</v>
       </c>
       <c r="G81" t="s">
@@ -15135,10 +15122,10 @@
       <c r="H81" t="s">
         <v>8</v>
       </c>
-      <c r="I81" vm="187">
+      <c r="I81" vm="185">
         <v>43.701944444444003</v>
       </c>
-      <c r="J81" vm="188">
+      <c r="J81" vm="186">
         <v>7.2683333333332998</v>
       </c>
     </row>
